--- a/important_mails_2026-09-30.xlsx
+++ b/important_mails_2026-09-30.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,113 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
+          <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (4sQeBGpWIe)</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 30 Sep 2026 08:58:18 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk
+ 96
+ We'll report and pay eco-contribution fees for your sales on Amazon.co.uk
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+ You’ve been enrolled </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (4sQeBGpWIe)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +626,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -582,39 +674,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -630,39 +722,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -678,39 +770,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -735,39 +827,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -783,39 +875,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -836,39 +928,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -884,39 +976,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -932,39 +1024,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -981,102 +1073,6 @@
 ------------------------------------------------------------------------------
 Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
 SPC-EUAmazon-299068859038264</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2547,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2566,178 +2562,21 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 01:51:02 +0000</t>
+          <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Actualización de estado de mercancías peligrosas</t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>96
- Actualización de estado de mercancías peligrosas
- Actualización de estado de mercancías peligrosas
- Estimado vendedor:
- Estamos llevando a cabo una revisión de mercancías peligrosas sobre uno o varios de tus productos:
- FALTA DOCUMENTACIÓN DE MERCANCÍAS PELIGROSAS O ES CONTRADICTORIA
- ASIN
- SKU del vendedor
- FNSKU
- Título
- B0HDVC3BVM
- WH-DE-811-WJJVINE-01
- Excavadora de Juguete 3 en 1 con Control Remoto para niños de 6 a 12 años, Control Remoto de 2.4 GHz, Accesorios metálicos y vehículo de orugas con rotación de 680° para Jugar al Aire Libre.
- ¿A qué se debe esto?
- No podemos clasificar correctamente los productos mencionados debido a que no tenemos suficiente información sobre las mercancías peligrosas. Ten en cuenta que, hasta que proporciones toda la información necesaria, los productos no estarán disponibles para la venta y no podrás continuar enviando unidades a los centros logísticos de Amazon. Tienes que proporcionar la ficha de datos de seguridad (FDS) de cada producto mencionado. Sólo puedes enviar una ficha de exención si el producto no tiene una FDS y no contiene productos químicos nocivos como alcohol, ácido, sodio, etc., o si el producto es una batería o las conti</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 01:45:44 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Status materiałów niebezpiecznych (hazmat)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>96
- Status materiałów niebezpiecznych (hazmat)
- Status materiałów niebezpiecznych (hazmat)
- Witamy w Fulfillment by Amazon
- Obecnie przeprowadzamy przegląd materiałów niebezpiecznych (hazmat) jednego produktu lub większej liczby produktów:
- SPRZECZNA LUB BRAKUJĄCA DOKUMENTACJA DG
- ASIN
- SKU sprzedawcy
- SKU sieci logistycznej
- Tytuł
- B0HDVC3BVM
- WH-DE-811-WJJVINE-01
- 3 w 1 zdalnie sterowana koparka dla dzieci w wieku od 6 do 12 lat z pilotem 2,4 GHz i metalowymi akcesoriami, gąsienicowy pojazd gąsienicowy 680° do zabawy w piaskownicy i na zewnątrz
- Jaka jest tego przyczyna
- Nie mamy wystarczającej ilości informacji o materiałach niebezpiecznych, aby prawidłowo sklasyfikować ww. produkty; dopóki nie dostarczysz niezbędnych informacji, produkty nie będą dostępne do sprzedaży i nie będziesz mógł wysłać więcej jednostek do centrów logistycznych Amazon. Musisz dostarczyć odpowiednią kartę charakterystyki dla każdego ww. produktu. Arkusz zwolnienia z obowiązku dostarczenia karty charakterystyki można złożyć tylko wtedy, kiedy produkt nie posiada szkodliwych substancji chemicznych, takich jak alkohol, kwas, sód itp., lub jeśli produkt jest bateriami, zawiera je lub jest sprzedawany z nimi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 01:03:52 +0000</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Aggiornamento dello stato delle merci pericolose</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Aggiornamento dello stato delle merci pericolose
- Aggiornamento dello stato delle merci pericolose
- Buongiorno da Logistica di Amazon.
- Al momento stiamo effettuando una revisione delle merci pericolose di uno o più dei suoi prodotti:
- DOCUMENTAZIONE MERCI PERICOLOSE DISCORDANTE O MANCANTE
- ASIN
- SKU venditore
- FNSKU
- Titolo
- B0HDVC3BVM
- WH-DE-811-WJJVINE-01
- Escavatore radiocomandato 3 in 1 per bambini dai 6 ai 12 anni, con telecomando a 2,4 GHz e accessori in metallo. Veicolo cingolato con rotazione a 680° per giocare nella sabbiera e all'aperto.
- Qual è il problema?
- Non disponiamo di informazioni sufficienti sulle merci pericolose per classificare correttamente i prodotti di cui sopra. Inoltre, finché non fornisci le informazioni necessarie, i prodotti non saranno disponibili per la vendita e non potrai inviare più unità ai centri logistici Amazon. Dovrai fornire una corretta scheda di sicurezza (SDS) per ogni prodotto sopra elencato. È possibile presentare una scheda di esenzione solo se il prodotto non dispone di una scheda di sicurezza e non contiene sostanze chimiche nocive, come alcol, acido, sodio e così via, o se il prodotto è, contiene o viene venduto con batterie.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2760,39 +2599,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-08</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2816,39 +2655,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2863,154 +2702,135 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的客户：
-您好！
-温馨提醒：收到贵司在亚马逊平台选择NBTS检测并提交了的 TR178989007592954 申请。
-为确保测试/验证流程顺利推进，请尽快联系我们完成信息确认。
-若 3 天内我们仍未收到贵司回应，我们将该 TRF 标记为 Unresponsive Seller（无响应卖家）。
-如后续仍需继续此 TRID 的测试与验证，可随时与我们联系并提交样品/测试报告，我们将协助该 TRF的后台状态更新。
-如有疑问，欢迎随时联系我们。
-谢谢！
-能标检测NBTS
---------------------------------------------------------------------
-Dear Valued Customer,
-Greetings!
-Friendly Reminder: We have received application TR178989007592954 submitted by your company, where NBTS was selected as the notified body on Amazon.
-To ensure the smooth progress of the testing and verification process, please contact us at your earliest convenience to complete information confirmation.
-If we do not receive your response within 3 days, this TRF will be marked as Unresponsive Seller.
-Should you need to resume testing and verification for this TRID at a later time, please feel free to contact us and submit samples / test reports. We will assist with updating the backend status of this TRF.
-Should you have any questions, please do not hesitate to contact us.
-Thank you!
-NBTS
------------------------------------
------------------------------------
-TEL:18998060978    TEL: 400-877-6107
-E-mail: fil.lin@nbtscn.com Web: www.nbtszg.com
-Add：广东省东</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Dangerous goods (hazmat) status update</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dangerous goods (hazmat) status update
- Dangerous goods (hazmat) status update
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
  Hello from Fulfillment by Amazon,
- We are currently conducting a dangerous goods (hazmat) review of one or more of your products:
- CONFLICTING OR MISSING DG DOCUMENTATION
- ASIN
- Merchant SKU
- FNSKU
- Title
- B0HDVC3BVM
- WH-DE-811-WJJVINE-01
- Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
- Why this is happening
- We do not have enough dangerous goods information to correctly classify the above products, and until you provide the necessary information, the products will not be available for sale and you will not be able to send more units to Amazon fulfillment centers. We need you to provide a proper Safety Data Sheet (SDS) for each product listed above. You may submit an exemption sheet only if the product does not have an SDS and does not contain any harmful chemicals, such as alcohol, acid, sodium, etc., or if the product is, contains, or is sold with batteries.
- How to continue selling these products
- Please make sure the SDS complies with the following re</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -3026,39 +2846,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3074,39 +2894,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3129,39 +2949,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3177,39 +2997,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3225,39 +3045,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3273,39 +3093,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3321,39 +3141,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3369,39 +3189,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3417,39 +3237,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3465,39 +3285,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3513,39 +3333,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3561,39 +3381,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3609,39 +3429,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3657,39 +3477,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3709,39 +3529,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3757,39 +3577,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3805,39 +3625,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3857,39 +3677,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3905,39 +3725,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3953,39 +3773,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4001,39 +3821,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4053,39 +3873,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4101,39 +3921,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4153,39 +3973,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4201,39 +4021,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4258,39 +4078,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -4303,39 +4123,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4351,39 +4171,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -4404,39 +4224,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -4452,39 +4272,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -4499,39 +4319,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4551,39 +4371,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 12:34:14 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Registration closes this Friday—save $200 with your exclusive code</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-15/7z5szk3/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5szk6/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
@@ -4597,39 +4417,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -4643,39 +4463,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4695,39 +4515,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4744,39 +4564,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4796,39 +4616,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>The Accelerate 2026 agenda got even better. See what's new.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
@@ -4846,39 +4666,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4898,39 +4718,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Discover sessions built for growing businesses, and save $200</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
@@ -4943,39 +4763,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4995,39 +4815,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5044,39 +4864,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5100,39 +4920,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -5148,39 +4968,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -5195,39 +5015,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5247,39 +5067,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5303,39 +5123,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1:1 expert access, new AI tools, and $200 off—register now</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
@@ -5351,40 +5171,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -5398,39 +5218,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -5446,39 +5266,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5494,39 +5314,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -5540,39 +5360,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5592,39 +5412,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5641,39 +5461,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5693,39 +5513,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -5734,39 +5554,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -5796,39 +5616,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:44:09 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>cscompliance-docreview-seller@amazon.de</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Problem gelöst (Anfrage Nr.: 13280404852)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 Problem gelöst (Anfrage Nr.: 13280404852)
@@ -5850,41 +5670,41 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:42:38 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY,
  MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document
  Review</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5902,40 +5722,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 08:56:32 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5960,39 +5780,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -6019,40 +5839,40 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit proof of insurance by January 18 to avoid listing
  deactivation</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -6068,40 +5888,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -6120,39 +5940,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -6174,39 +5994,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6224,39 +6044,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6274,39 +6094,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 08:06:37 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6324,39 +6144,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 17:08:09 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6374,39 +6194,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:07:40 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6424,39 +6244,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:40 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6475,39 +6295,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:40:10 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -6520,39 +6340,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:27 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6571,39 +6391,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:04 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6621,39 +6441,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:08:31 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6670,39 +6490,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:59:58 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6720,39 +6540,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:32 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6770,39 +6590,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6818,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6868,39 +6688,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6918,39 +6738,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 13:10:03 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6967,39 +6787,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:30:25 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7017,39 +6837,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:14:40 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7067,39 +6887,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 12:45:43 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7115,39 +6935,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 20:11:48 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7165,39 +6985,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 19:56:44 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7215,39 +7035,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:41:56 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -7256,39 +7076,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 16:03:11 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -7330,6 +7150,163 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:51:02 +0000</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Actualización de estado de mercancías peligrosas</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Actualización de estado de mercancías peligrosas
+ Actualización de estado de mercancías peligrosas
+ Estimado vendedor:
+ Estamos llevando a cabo una revisión de mercancías peligrosas sobre uno o varios de tus productos:
+ FALTA DOCUMENTACIÓN DE MERCANCÍAS PELIGROSAS O ES CONTRADICTORIA
+ ASIN
+ SKU del vendedor
+ FNSKU
+ Título
+ B0HDVC3BVM
+ WH-DE-811-WJJVINE-01
+ Excavadora de Juguete 3 en 1 con Control Remoto para niños de 6 a 12 años, Control Remoto de 2.4 GHz, Accesorios metálicos y vehículo de orugas con rotación de 680° para Jugar al Aire Libre.
+ ¿A qué se debe esto?
+ No podemos clasificar correctamente los productos mencionados debido a que no tenemos suficiente información sobre las mercancías peligrosas. Ten en cuenta que, hasta que proporciones toda la información necesaria, los productos no estarán disponibles para la venta y no podrás continuar enviando unidades a los centros logísticos de Amazon. Tienes que proporcionar la ficha de datos de seguridad (FDS) de cada producto mencionado. Sólo puedes enviar una ficha de exención si el producto no tiene una FDS y no contiene productos químicos nocivos como alcohol, ácido, sodio, etc., o si el producto es una batería o las conti</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:45:44 +0000</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Status materiałów niebezpiecznych (hazmat)</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Status materiałów niebezpiecznych (hazmat)
+ Status materiałów niebezpiecznych (hazmat)
+ Witamy w Fulfillment by Amazon
+ Obecnie przeprowadzamy przegląd materiałów niebezpiecznych (hazmat) jednego produktu lub większej liczby produktów:
+ SPRZECZNA LUB BRAKUJĄCA DOKUMENTACJA DG
+ ASIN
+ SKU sprzedawcy
+ SKU sieci logistycznej
+ Tytuł
+ B0HDVC3BVM
+ WH-DE-811-WJJVINE-01
+ 3 w 1 zdalnie sterowana koparka dla dzieci w wieku od 6 do 12 lat z pilotem 2,4 GHz i metalowymi akcesoriami, gąsienicowy pojazd gąsienicowy 680° do zabawy w piaskownicy i na zewnątrz
+ Jaka jest tego przyczyna
+ Nie mamy wystarczającej ilości informacji o materiałach niebezpiecznych, aby prawidłowo sklasyfikować ww. produkty; dopóki nie dostarczysz niezbędnych informacji, produkty nie będą dostępne do sprzedaży i nie będziesz mógł wysłać więcej jednostek do centrów logistycznych Amazon. Musisz dostarczyć odpowiednią kartę charakterystyki dla każdego ww. produktu. Arkusz zwolnienia z obowiązku dostarczenia karty charakterystyki można złożyć tylko wtedy, kiedy produkt nie posiada szkodliwych substancji chemicznych, takich jak alkohol, kwas, sód itp., lub jeśli produkt jest bateriami, zawiera je lub jest sprzedawany z nimi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:03:52 +0000</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Aggiornamento dello stato delle merci pericolose</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Aggiornamento dello stato delle merci pericolose
+ Aggiornamento dello stato delle merci pericolose
+ Buongiorno da Logistica di Amazon.
+ Al momento stiamo effettuando una revisione delle merci pericolose di uno o più dei suoi prodotti:
+ DOCUMENTAZIONE MERCI PERICOLOSE DISCORDANTE O MANCANTE
+ ASIN
+ SKU venditore
+ FNSKU
+ Titolo
+ B0HDVC3BVM
+ WH-DE-811-WJJVINE-01
+ Escavatore radiocomandato 3 in 1 per bambini dai 6 ai 12 anni, con telecomando a 2,4 GHz e accessori in metallo. Veicolo cingolato con rotazione a 680° per giocare nella sabbiera e all'aperto.
+ Qual è il problema?
+ Non disponiamo di informazioni sufficienti sulle merci pericolose per classificare correttamente i prodotti di cui sopra. Inoltre, finché non fornisci le informazioni necessarie, i prodotti non saranno disponibili per la vendita e non potrai inviare più unità ai centri logistici Amazon. Dovrai fornire una corretta scheda di sicurezza (SDS) per ogni prodotto sopra elencato. È possibile presentare una scheda di esenzione solo se il prodotto non dispone di una scheda di sicurezza e non contiene sostanze chimiche nocive, come alcol, acido, sodio e così via, o se il prodotto è, contiene o viene venduto con batterie.
+</t>
+        </is>
+      </c>
+    </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
@@ -12975,7 +12952,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
+          <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -12990,6 +12967,121 @@
       </c>
       <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的客户：
+您好！
+温馨提醒：收到贵司在亚马逊平台选择NBTS检测并提交了的 TR178989007592954 申请。
+为确保测试/验证流程顺利推进，请尽快联系我们完成信息确认。
+若 3 天内我们仍未收到贵司回应，我们将该 TRF 标记为 Unresponsive Seller（无响应卖家）。
+如后续仍需继续此 TRID 的测试与验证，可随时与我们联系并提交样品/测试报告，我们将协助该 TRF的后台状态更新。
+如有疑问，欢迎随时联系我们。
+谢谢！
+能标检测NBTS
+--------------------------------------------------------------------
+Dear Valued Customer,
+Greetings!
+Friendly Reminder: We have received application TR178989007592954 submitted by your company, where NBTS was selected as the notified body on Amazon.
+To ensure the smooth progress of the testing and verification process, please contact us at your earliest convenience to complete information confirmation.
+If we do not receive your response within 3 days, this TRF will be marked as Unresponsive Seller.
+Should you need to resume testing and verification for this TRID at a later time, please feel free to contact us and submit samples / test reports. We will assist with updating the backend status of this TRF.
+Should you have any questions, please do not hesitate to contact us.
+Thank you!
+NBTS
+-----------------------------------
+-----------------------------------
+TEL:18998060978    TEL: 400-877-6107
+E-mail: fil.lin@nbtscn.com Web: www.nbtszg.com
+Add：广东省东</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Dangerous goods (hazmat) status update</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dangerous goods (hazmat) status update
+ Dangerous goods (hazmat) status update
+ Hello from Fulfillment by Amazon,
+ We are currently conducting a dangerous goods (hazmat) review of one or more of your products:
+ CONFLICTING OR MISSING DG DOCUMENTATION
+ ASIN
+ Merchant SKU
+ FNSKU
+ Title
+ B0HDVC3BVM
+ WH-DE-811-WJJVINE-01
+ Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
+ Why this is happening
+ We do not have enough dangerous goods information to correctly classify the above products, and until you provide the necessary information, the products will not be available for sale and you will not be able to send more units to Amazon fulfillment centers. We need you to provide a proper Safety Data Sheet (SDS) for each product listed above. You may submit an exemption sheet only if the product does not have an SDS and does not contain any harmful chemicals, such as alcohol, acid, sodium, etc., or if the product is, contains, or is sold with batteries.
+ How to continue selling these products
+ Please make sure the SDS complies with the following re</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13017,40 +13109,40 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -13065,39 +13157,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13125,39 +13217,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -13173,39 +13265,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -13228,39 +13320,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13288,39 +13380,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -13335,40 +13427,40 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -13385,39 +13477,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 00:17:14 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
